--- a/Gestión de Producción/Corrección de entrega/Analisis Financiero (Preliminar).xlsx
+++ b/Gestión de Producción/Corrección de entrega/Analisis Financiero (Preliminar).xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manto\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Compa\Documents\2026A\APM\Proyecto-APM---2026-1S\Gestión de Producción\Corrección de entrega\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{87EE9D1F-51F7-40FA-8A06-12E265836CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{34CA9882-19DA-4025-A6B3-A5B193287BD3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{34CA9882-19DA-4025-A6B3-A5B193287BD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Adquisiciones" sheetId="1" r:id="rId1"/>
     <sheet name="EX+B" sheetId="2" r:id="rId2"/>
     <sheet name="FdC" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -133,10 +144,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -240,59 +251,59 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -316,7 +327,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -428,7 +439,7 @@
             <c:numRef>
               <c:f>FdC!$B$2:$B$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
+                <c:formatCode>"$"\ #,##0.00;[Red]\-"$"\ #,##0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>-278129087</c:v>
@@ -527,7 +538,7 @@
             <c:numRef>
               <c:f>FdC!$C$2:$C$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:formatCode>"$"\ #,##0;[Red]\-"$"\ #,##0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -626,7 +637,7 @@
             <c:numRef>
               <c:f>FdC!$D$2:$D$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:formatCode>"$"\ #,##0;[Red]\-"$"\ #,##0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>-278129087</c:v>
@@ -725,7 +736,7 @@
             <c:numRef>
               <c:f>FdC!$E$2:$E$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:formatCode>"$"\ #,##0;[Red]\-"$"\ #,##0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>-278129087</c:v>
@@ -1701,9 +1712,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1741,7 +1752,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1847,7 +1858,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1989,7 +2000,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1998,15 +2009,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC626771-BBF1-4BDA-AE97-3F55ED6FC1BC}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="52.7109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="18.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="231.85546875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="52.6640625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="18.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="231.88671875" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
@@ -2020,7 +2031,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2028,7 +2039,7 @@
         <f>188299170+50000000</f>
         <v>238299170</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="19">
         <f t="shared" ref="C2" si="0">B2*1.1</f>
         <v>262129087.00000003</v>
       </c>
@@ -2036,15 +2047,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2053,34 +2064,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B1E273-002F-44CB-B87B-B9FBB131734B}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="30.28515625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="4"/>
-    <col min="7" max="7" width="45.140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="4"/>
+    <col min="7" max="7" width="45.109375" style="4" customWidth="1"/>
     <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="4"/>
+    <col min="9" max="16384" width="11.44140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="20"/>
+      <c r="D1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="G1" s="10" t="s">
+      <c r="E1" s="20"/>
+      <c r="G1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="10"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -2100,7 +2111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2133,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -2145,7 +2156,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2167,7 +2178,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -2182,7 +2193,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <f>SUM(B3:B6)</f>
         <v>53400000</v>
@@ -2209,498 +2220,498 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4FD7C4-7C36-405F-988D-68A540A30D5D}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" style="6" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="16" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="4"/>
+    <col min="2" max="2" width="17.88671875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="15" customWidth="1"/>
+    <col min="6" max="16384" width="11.44140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="7">
         <f>'EX+B'!E7*-1</f>
         <v>-278129087</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="15">
         <v>0</v>
       </c>
-      <c r="D2" s="16">
-        <f>SUM(B2:C2)</f>
+      <c r="D2" s="15">
+        <f t="shared" ref="D2:D21" si="0">SUM(B2:C2)</f>
         <v>-278129087</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="15">
         <f>D2</f>
         <v>-278129087</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="7">
         <f>'EX+B'!B7*-1</f>
         <v>-53400000</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <f>'EX+B'!H7</f>
         <v>73000000</v>
       </c>
-      <c r="D3" s="16">
-        <f>SUM(B3:C3)</f>
+      <c r="D3" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="15">
         <f>E2+D3</f>
         <v>-258529087</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="7">
         <f>B3</f>
         <v>-53400000</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="15">
         <f>C3</f>
         <v>73000000</v>
       </c>
-      <c r="D4" s="16">
-        <f>SUM(B4:C4)</f>
+      <c r="D4" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E4" s="16">
-        <f t="shared" ref="E4:E21" si="0">E3+D4</f>
+      <c r="E4" s="15">
+        <f t="shared" ref="E4:E21" si="1">E3+D4</f>
         <v>-238929087</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
       <c r="B5" s="7">
-        <f t="shared" ref="B4:B20" si="1">B4</f>
+        <f t="shared" ref="B5:B19" si="2">B4</f>
         <v>-53400000</v>
       </c>
-      <c r="C5" s="16">
-        <f t="shared" ref="C5:C21" si="2">C4</f>
+      <c r="C5" s="15">
+        <f t="shared" ref="C5:C21" si="3">C4</f>
         <v>73000000</v>
       </c>
-      <c r="D5" s="16">
-        <f>SUM(B5:C5)</f>
+      <c r="D5" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
+        <f t="shared" si="1"/>
+        <v>-219329087</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C6" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D6" s="15">
         <f t="shared" si="0"/>
-        <v>-219329087</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
+        <v>19600000</v>
+      </c>
+      <c r="E6" s="15">
         <f t="shared" si="1"/>
+        <v>-199729087</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7">
+        <f t="shared" si="2"/>
         <v>-53400000</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C7" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D7" s="15">
+        <f t="shared" si="0"/>
+        <v>19600000</v>
+      </c>
+      <c r="E7" s="15">
+        <f t="shared" si="1"/>
+        <v>-180129087</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7">
         <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C8" s="15">
+        <f t="shared" si="3"/>
         <v>73000000</v>
       </c>
-      <c r="D6" s="16">
-        <f>SUM(B6:C6)</f>
+      <c r="D8" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E8" s="15">
+        <f t="shared" si="1"/>
+        <v>-160529087</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7">
+        <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C9" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D9" s="15">
         <f t="shared" si="0"/>
-        <v>-199729087</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7">
+        <v>19600000</v>
+      </c>
+      <c r="E9" s="15">
         <f t="shared" si="1"/>
+        <v>-140929087</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <f t="shared" si="2"/>
         <v>-53400000</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C10" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D10" s="15">
+        <f t="shared" si="0"/>
+        <v>19600000</v>
+      </c>
+      <c r="E10" s="15">
+        <f t="shared" si="1"/>
+        <v>-121329087</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7">
         <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C11" s="15">
+        <f t="shared" si="3"/>
         <v>73000000</v>
       </c>
-      <c r="D7" s="16">
-        <f>SUM(B7:C7)</f>
+      <c r="D11" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E11" s="15">
+        <f t="shared" si="1"/>
+        <v>-101729087</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7">
+        <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C12" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D12" s="15">
         <f t="shared" si="0"/>
-        <v>-180129087</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7">
+        <v>19600000</v>
+      </c>
+      <c r="E12" s="15">
         <f t="shared" si="1"/>
+        <v>-82129087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7">
+        <f t="shared" si="2"/>
         <v>-53400000</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C13" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D13" s="15">
+        <f t="shared" si="0"/>
+        <v>19600000</v>
+      </c>
+      <c r="E13" s="15">
+        <f t="shared" si="1"/>
+        <v>-62529087</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7">
         <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" si="3"/>
         <v>73000000</v>
       </c>
-      <c r="D8" s="16">
-        <f>SUM(B8:C8)</f>
+      <c r="D14" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E14" s="15">
+        <f t="shared" si="1"/>
+        <v>-42929087</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7">
+        <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C15" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D15" s="15">
         <f t="shared" si="0"/>
-        <v>-160529087</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7">
+        <v>19600000</v>
+      </c>
+      <c r="E15" s="15">
         <f t="shared" si="1"/>
+        <v>-23329087</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7">
+        <f t="shared" si="2"/>
         <v>-53400000</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C16" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D16" s="15">
+        <f t="shared" si="0"/>
+        <v>19600000</v>
+      </c>
+      <c r="E16" s="15">
+        <f t="shared" si="1"/>
+        <v>-3729087</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7">
         <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C17" s="15">
+        <f t="shared" si="3"/>
         <v>73000000</v>
       </c>
-      <c r="D9" s="16">
-        <f>SUM(B9:C9)</f>
+      <c r="D17" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E17" s="15">
+        <f t="shared" si="1"/>
+        <v>15870913</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7">
+        <f t="shared" si="2"/>
+        <v>-53400000</v>
+      </c>
+      <c r="C18" s="15">
+        <f t="shared" si="3"/>
+        <v>73000000</v>
+      </c>
+      <c r="D18" s="15">
         <f t="shared" si="0"/>
-        <v>-140929087</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7">
+        <v>19600000</v>
+      </c>
+      <c r="E18" s="15">
         <f t="shared" si="1"/>
+        <v>35470913</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7">
+        <f t="shared" si="2"/>
         <v>-53400000</v>
       </c>
-      <c r="C10" s="16">
-        <f t="shared" si="2"/>
+      <c r="C19" s="15">
+        <f t="shared" si="3"/>
         <v>73000000</v>
       </c>
-      <c r="D10" s="16">
-        <f>SUM(B10:C10)</f>
+      <c r="D19" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E10" s="16">
-        <f t="shared" si="0"/>
-        <v>-121329087</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7">
+      <c r="E19" s="15">
         <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C11" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D11" s="16">
-        <f>SUM(B11:C11)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E11" s="16">
-        <f t="shared" si="0"/>
-        <v>-101729087</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C12" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D12" s="16">
-        <f>SUM(B12:C12)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E12" s="16">
-        <f t="shared" si="0"/>
-        <v>-82129087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C13" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D13" s="16">
-        <f>SUM(B13:C13)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E13" s="16">
-        <f t="shared" si="0"/>
-        <v>-62529087</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C14" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D14" s="16">
-        <f>SUM(B14:C14)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E14" s="16">
-        <f t="shared" si="0"/>
-        <v>-42929087</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C15" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D15" s="16">
-        <f>SUM(B15:C15)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E15" s="16">
-        <f t="shared" si="0"/>
-        <v>-23329087</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C16" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D16" s="16">
-        <f>SUM(B16:C16)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E16" s="16">
-        <f t="shared" si="0"/>
-        <v>-3729087</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C17" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D17" s="16">
-        <f>SUM(B17:C17)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E17" s="16">
-        <f t="shared" si="0"/>
-        <v>15870913</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C18" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D18" s="16">
-        <f>SUM(B18:C18)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E18" s="16">
-        <f t="shared" si="0"/>
-        <v>35470913</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7">
-        <f t="shared" si="1"/>
-        <v>-53400000</v>
-      </c>
-      <c r="C19" s="16">
-        <f t="shared" si="2"/>
-        <v>73000000</v>
-      </c>
-      <c r="D19" s="16">
-        <f>SUM(B19:C19)</f>
-        <v>19600000</v>
-      </c>
-      <c r="E19" s="16">
-        <f t="shared" si="0"/>
         <v>55070913</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
         <v>19</v>
       </c>
       <c r="B20" s="7">
         <f>B19</f>
         <v>-53400000</v>
       </c>
-      <c r="C20" s="16">
-        <f t="shared" si="2"/>
+      <c r="C20" s="15">
+        <f t="shared" si="3"/>
         <v>73000000</v>
       </c>
-      <c r="D20" s="16">
-        <f>SUM(B20:C20)</f>
+      <c r="D20" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E20" s="16">
-        <f t="shared" si="0"/>
+      <c r="E20" s="15">
+        <f t="shared" si="1"/>
         <v>74670913</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
         <v>19</v>
       </c>
       <c r="B21" s="7">
         <f>B20</f>
         <v>-53400000</v>
       </c>
-      <c r="C21" s="16">
-        <f t="shared" si="2"/>
+      <c r="C21" s="15">
+        <f t="shared" si="3"/>
         <v>73000000</v>
       </c>
-      <c r="D21" s="16">
-        <f>SUM(B21:C21)</f>
+      <c r="D21" s="15">
+        <f t="shared" si="0"/>
         <v>19600000</v>
       </c>
-      <c r="E21" s="16">
-        <f t="shared" si="0"/>
+      <c r="E21" s="15">
+        <f t="shared" si="1"/>
         <v>94270913</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="20"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="B24" s="22"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="16">
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <f>-E17/D2</f>
         <v>5.7063118321026236E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <f>IRR(D2:D17)</f>
         <v>7.0183778708419187E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="17">
         <f>A16+(-E16/D16)</f>
         <v>15.190259540816326</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="18">
         <f>NPV(B25,D3:D21)+D2</f>
         <v>-116855576.25684595</v>
       </c>
